--- a/config/loading_tips.xlsx
+++ b/config/loading_tips.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="loading_tips" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="loading_tips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1095,10 +1095,6 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tips：メイン画面で、仲間をタップすると、報酬を貰えるかも！？</t>
+          <t>Tips：在主画面中，点击伙伴的话，可能会获得报酬哦！?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1158,7 +1154,6 @@
           <t>알림: 메인 지역에는 부끄러운 따라큐가 가끔씩 나타납니다.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1168,7 +1163,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tips：ステージを掃討すると、神秘商店が出現するかも！？</t>
+          <t>Tips：扫荡关卡时，可能会出现神秘商店！?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1186,7 +1181,6 @@
           <t>"알림: 메타몽은 다른 친구들과 놀고 싶어하지만, 아직 눈까지 바꾸는 법은 모르는 듯합니다."</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1196,7 +1190,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tips：立絵のバフの効果は、解放時から有効になります。</t>
+          <t>Tips：立绘的增益效果从解放时开始生效。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1214,7 +1208,6 @@
           <t>알림: 개인 아바타 보너스의 속성은 개방 즉시 적용됩니다.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1224,7 +1217,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tips：仲間の図鑑を解放すると、その仲間をアイコンに設定できるかも！</t>
+          <t>Tips：解放伙伴图鉴的话，说不定可以将伙伴设定为图标！</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1242,7 +1235,6 @@
           <t>알림: 포켓몬 도감 개방 시 해당 포켓몬을 프로필로 사용할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1252,7 +1244,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tips：設定からFPSを変更できます。</t>
+          <t>提示：您可以从设置更改FPS。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1270,7 +1262,6 @@
           <t>알림: 설정에서 프레임을 설정할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1280,7 +1271,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Tips：期間限定の称号は、使用期限内のみ装備できます。</t>
+          <t>Tips：期间限定的称号只能在使用期限内装备。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,7 +1289,6 @@
           <t>알림: 한정 호칭이 만료되면 사용할 수 없습니다.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1308,7 +1298,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Tips：出現の神秘商店はどこだって？メイン画面に訪れた美少女をタップしよう！</t>
+          <t>Tips：出现的神秘商店在哪里？点击主画面访问的美少女吧！</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1326,7 +1316,6 @@
           <t>알림: 누군가 스테이지를 클리어한 후 신비한 상점을 발견했다고 합니다.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1336,7 +1325,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tips：スタミナを長押しすると、回復状況の詳細を確認できます！</t>
+          <t>Tips：长按耐力可以查看恢复状态的详细信息！</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1354,7 +1343,6 @@
           <t>알림: 체력 바를 길게 터치하면 체력 회복 상황을 확인할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1364,7 +1352,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tips：ステージをクリアする時、マップ上の宝箱も忘れずに受け取りましょう！</t>
+          <t>Tips：通关关卡时，别忘了领取地图上的宝箱哦！</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1382,7 +1370,6 @@
           <t>알림: 스테이지 클리어 후 지도에 떨어진 보물상자가 없는지 살펴보세요.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1392,7 +1379,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tips：冒険で毎日更新される日常ダンジョンを確認しましょう。</t>
+          <t>技巧：查看每日更新的日常地牢冒险。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1410,7 +1397,6 @@
           <t>알림: 매일 보상 던전을 절대 잊지 마세요.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1420,7 +1406,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tips：育成支援では育成支援箱を獲得できますよ！</t>
+          <t>Tips：育成支援可以获得育成支援箱哦！</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1438,7 +1424,6 @@
           <t>알림: 코인 이벤트에서는 입히는 피해가 클수록 획득하는 코인이 증가합니다.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1448,7 +1433,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tips：ギフトダンジョンでは、毎日違う制限ルールが設けられます。</t>
+          <t>Tips：礼物地下城每天都有不同的限制规则。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1466,7 +1451,6 @@
           <t>알림: 선물 이벤트의 몬스터는 가끔씩 피해 또는 특수공격 피해에 면역되니 잘 확인해야 합니다.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1476,7 +1460,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Tips：日常ダンジョンはステージのクリア進捗が100%で次のステージが解放されます。</t>
+          <t>Tips：日常迷宫关卡的通关进度100%会释放下一个关卡。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1494,7 +1478,6 @@
           <t>알림: 조각 이벤트와 같은 계열의 포켓몬을 사용해 도전하면 추가 보상을 획득할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1504,7 +1487,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Tips：複数の編成を事前に保存して自由に切替できます。</t>
+          <t>技巧：可以预先保存多个组合并自由切换。</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1522,7 +1505,6 @@
           <t>알림: 메인 시티 라인업을 아레나 방어 라인업에 자주 동기화해줘야 합니다.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1532,7 +1514,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tips：ギルドに加入して、仲間たちと一緒に戦いましょう。</t>
+          <t>Tips：加入公会，和伙伴们一起战斗吧。</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1532,6 @@
           <t>알림: 어서 길드에 가입해 뜻이 맞는 동료들을 만나 보세요.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1560,7 +1541,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tips：仲間のレベルは、プレイヤーレベルを超えることはできません。</t>
+          <t>技巧：伙伴的等级不能超过玩家等级。</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1578,7 +1559,6 @@
           <t>알림: 포켓몬 레벨은 트레이너 레벨보다 높을 수 없습니다.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1588,7 +1568,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Tips：ギルドダンジョンの報酬は、画面右下から受け取れます。</t>
+          <t>Tips：公会地下城的报酬可以从画面右下方领取。</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1606,7 +1586,6 @@
           <t>알림: 길드 던전의 클리어 보상은 모두 우측 하단에 있습니다.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1616,7 +1595,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Tips：訓練センターの仲間は、1日6回まで加速助力ができます。</t>
+          <t>Tips：训练中心的伙伴每天最多可以提供6次加速助力。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1634,7 +1613,6 @@
           <t>알림: 훈련 센터의 단일 포켓몬은 매일 최대 6회 가속 경험치를 획득할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1644,7 +1622,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tips：ギフトは無料で配布できます。獲得したらみんなに配布しましょう。</t>
+          <t>Tips：礼品可以免费分发。获得后再分发给大家。</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1662,7 +1640,6 @@
           <t>알림: 보너스 획득 시 발송하는 것을 잊지 마세요. 보너스 발송은 무료입니다.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1672,7 +1649,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Tips：ギルド脱退当日、他のギルドに加入すると一部のギルド機能が翌日から使用できます。</t>
+          <t>Tips：退出公会当天加入其他公会的话，部分公会功能可以从第二天开始使用。</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1690,7 +1667,6 @@
           <t>알림: 길드 변경 시 일부 건물은 당일에 사용할 수 없습니다.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1700,7 +1676,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tips：オンライン報酬で「受取可能」と表示したらタップしましょう！</t>
+          <t>Tips：在线奖励显示“可领取”时点击！</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1718,7 +1694,6 @@
           <t>알림: 전설에 따르면 칠색조를 본 사람은 영원한 행복이 약속된다고 합니다.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1728,7 +1703,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Tips：プレイヤーレベル20で、戦闘の3倍速が解放されます。</t>
+          <t>技巧：玩家等级20释放战斗速度的3倍。</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1746,7 +1721,6 @@
           <t>알림: 유저가 20레벨을 달성하면 전투 3배속을 개방할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1756,7 +1730,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tips：仲間に様々な性格があります。性格は仲間獲得時にランダムで付与されます。</t>
+          <t>Tips：伙伴有各种各样的性格。性格在获得伙伴时随机被赋予。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1748,6 @@
           <t>알림: 포켓몬에게 가방 안의 민트를 사용하면 지정한 성격을 획득할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1784,7 +1757,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Tips：プレイヤーレベル35で、スキルの高速LvUPが解放されます。</t>
+          <t>技巧：玩家等级35时，技能的高速LvUP会被释放。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1802,7 +1775,6 @@
           <t>알림: 유저 35레벨 달성 시 기술의 빠른 레벨업 기능이 개방됩니다.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1812,7 +1784,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tips：仲間の名前を自由に変更できますよ。</t>
+          <t>Tips：可以自由更改伙伴的名字哦。</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1830,7 +1802,6 @@
           <t>알림: 휴대 아이템은 포켓몬과 동일하게 부활할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1840,7 +1811,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Tips：仲間の性格を変更できるアイテムも存在しますよ。</t>
+          <t>Tips：也有可以改变伙伴性格的道具哦。</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1858,7 +1829,6 @@
           <t>"알림: 가방에 민트가 없을 경우, 아이템 성격 변경 기능이 자동으로 숨겨집니다."</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1868,7 +1838,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tips：図鑑から仲間の進化分岐を確認できます。</t>
+          <t>Tips：从图鉴中可以确认伙伴的进化分支。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1886,7 +1856,6 @@
           <t>알림: 도감에 보이지 않는 포켓몬도 이후 추가될 수 있습니다.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1896,7 +1865,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Tips：エッグモンは対象レア度の任意仲間の本体素材として使えますよ。</t>
+          <t>Tips：蛋兽可以作为对象稀有度的任意伙伴的本体素材使用哦。</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1914,7 +1883,6 @@
           <t>알림:전설의 포켓몬 만능 조각,현재로서  과학 기술 수준으로는 다시 일반 만능 조각으로 전환할 수 없습니다.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1924,7 +1892,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Tips：レベル36で仲間招待が解放します。</t>
+          <t>技巧：等级36时邀请伙伴即可解放。</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1942,7 +1910,6 @@
           <t>알림: 36레벨 이후 체력 사용 시 일정 확률로 포획 가능한 포켓몬을 발견합니다.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1952,7 +1919,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Tips：PvPでは、同仲間同速度の場合、行動順がランダムになります。</t>
+          <t>Tips：在PvP中，同伙伴同速度的情况下，行动顺序会随机。</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1970,7 +1937,6 @@
           <t>알림:대전 아레나 경기중에 같은 포켓몬이나 같은 속도의 두 포켓몬의 행동 순서는 순전히 무작위이다.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
